--- a/testcases/testcases_vanphongdientu.xlsx
+++ b/testcases/testcases_vanphongdientu.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>❖ BẢNG QUYẾT ĐỊNH (DECISION TABLE) - ĐĂNG NHẬP VĂN PHÒNG ĐIỆN TỬ UTC</t>
+          <t>BANG QUYET DINH (DECISION TABLE) - DANG NHAP VAN PHONG DIEN TU UTC</t>
         </is>
       </c>
     </row>
